--- a/outputs/09_alternative_robustness_models/alternative_robustness_summary.xlsx
+++ b/outputs/09_alternative_robustness_models/alternative_robustness_summary.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_check" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_reference" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ordered_logit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alternative_dv" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="weighted_ols" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="low_dmi_subsample" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alternative_ai_measure" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="long_results" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="report_table" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fit_stats" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="variable_check" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="main_reference" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ordered_logit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="alternative_dv" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="weighted_ols" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="low_dmi_subsample" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="alternative_ai_measure" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="long_results" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="report_table" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="fit_stats" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,16 +26,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,21 +51,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,27 +426,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>변수명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>존재 여부</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>유효 N</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>결측 N</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>dtype</t>
         </is>
@@ -732,52 +720,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형 유형</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Adj. R²</t>
         </is>
@@ -1744,82 +1732,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>유의수준</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>주모형 방향과 일치 여부</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>주모형 유의성과 일치 여부</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2202,82 +2190,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>유의수준</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>주모형 방향과 일치 여부</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>주모형 유의성과 일치 여부</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2660,82 +2648,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>유의수준</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>주모형 방향과 일치 여부</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>주모형 유의성과 일치 여부</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3122,82 +3110,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>유의수준</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>주모형 방향과 일치 여부</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>주모형 유의성과 일치 여부</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3580,82 +3568,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>유의수준</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>주모형 방향과 일치 여부</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>주모형 유의성과 일치 여부</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3816,82 +3804,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>유의수준</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>주모형 방향과 일치 여부</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>주모형 유의성과 일치 여부</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3986,82 +3974,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>분석 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>모형명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>유의수준</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>주모형 방향과 일치 여부</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>주모형 유의성과 일치 여부</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>결론</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -5748,52 +5736,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>가설</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>보조모형 구분</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>종속변수</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>핵심 계수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>계수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>적합도</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>주모형 일치 여부</t>
         </is>
